--- a/data/trans_orig/CAGE-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2007</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>10369</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>9837</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1015528</t>
+          <t>1014983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1027836</t>
+          <t>1027700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1304550</t>
+          <t>1303185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2325990</t>
+          <t>2325236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2340975</t>
+          <t>2341267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>5722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>17333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7793</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1669878</t>
+          <t>1670911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1685327</t>
+          <t>1686147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1577155</t>
+          <t>1577370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1586505</t>
+          <t>1586659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3253322</t>
+          <t>3253099</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3270429</t>
+          <t>3270138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1871,97 +1871,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541655</t>
+          <t>541780</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550558</t>
+          <t>550560</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>468645</t>
+          <t>469227</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1015322</t>
+          <t>1015008</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025827</t>
+          <t>1025937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16772</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>30430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,47 +2829,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2012</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>943934</t>
+          <t>944069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>964607</t>
+          <t>964758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1335738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1337797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2282632</t>
+          <t>2281960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2302670</t>
+          <t>2302370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6486</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,49 +3937,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5731</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5016</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>14</t>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35760</t>
+          <t>35794</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41881</t>
+          <t>39841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1907398</t>
+          <t>1907575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1932945</t>
+          <t>1933209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1746161</t>
+          <t>1745485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1755796</t>
+          <t>1755805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3660082</t>
+          <t>3660442</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3686498</t>
+          <t>3687297</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -4378,97 +4378,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2104</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>854</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>10667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,62 +4639,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2186</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>12445</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>465560</t>
+          <t>466716</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479471</t>
+          <t>480038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>920430</t>
+          <t>924111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>937828</t>
+          <t>938114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,47 +4997,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>8882</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>4219</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>17261</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>8882</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>15179</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34597</t>
+          <t>33831</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34157</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>50162</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>55184</t>
+          <t>53885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3333519</t>
+          <t>3334814</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3369092</t>
+          <t>3369554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3542246</t>
+          <t>3542918</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3552239</t>
+          <t>3552237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6883684</t>
+          <t>6884016</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6918703</t>
+          <t>6919031</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2016</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10136</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>727228</t>
+          <t>726822</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>745058</t>
+          <t>744500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>987416</t>
+          <t>988881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1720228</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1738921</t>
+          <t>1738623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,62 +6351,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4219</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4128</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11536</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3923</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39444</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2034488</t>
+          <t>2034944</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2057193</t>
+          <t>2057238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1971593</t>
+          <t>1970883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1983914</t>
+          <t>1983962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4012143</t>
+          <t>4014730</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4037619</t>
+          <t>4039179</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -6885,97 +6885,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4624</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>922</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4963</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -6998,97 +6998,97 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19229</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>532598</t>
+          <t>534297</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545927</t>
+          <t>545929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534482</t>
+          <t>534622</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>546347</t>
+          <t>546344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1075334</t>
+          <t>1075976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091220</t>
+          <t>1091080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7174</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22715</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23197</t>
+          <t>22149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>24034</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>47733</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34904</t>
+          <t>34914</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65012</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3312049</t>
+          <t>3312448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3342034</t>
+          <t>3340528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3505329</t>
+          <t>3504497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3522449</t>
+          <t>3522732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6824329</t>
+          <t>6825273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6859794</t>
+          <t>6858925</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sospecha de alcoholismo (CAGE) en 2023</t>
+          <t>Población con sospecha de alcoholismo (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>219056</t>
+          <t>219017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>235120</t>
+          <t>234851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285176</t>
+          <t>284652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301194</t>
+          <t>301222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11268</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>1675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>959630</t>
+          <t>959859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>974360</t>
+          <t>974342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>685240</t>
+          <t>685141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>701875</t>
+          <t>701346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1651148</t>
+          <t>1652059</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1672658</t>
+          <t>1673196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11051</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326852</t>
+          <t>327284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338482</t>
+          <t>338513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>233838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239962</t>
+          <t>239914</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>565289</t>
+          <t>564800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>577482</t>
+          <t>577438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>560</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24455</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1517204</t>
+          <t>1517171</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1541717</t>
+          <t>1541619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>989035</t>
+          <t>989982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1006721</t>
+          <t>1007144</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2516387</t>
+          <t>2516151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2547553</t>
+          <t>2547434</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CAGE-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1014983</t>
+          <t>1014477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1027700</t>
+          <t>1027767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1303185</t>
+          <t>1304323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2325236</t>
+          <t>2325697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2341267</t>
+          <t>2340813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17333</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19502</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1670911</t>
+          <t>1670397</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1686147</t>
+          <t>1685752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1577370</t>
+          <t>1577547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1586659</t>
+          <t>1586504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3253099</t>
+          <t>3253797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3270138</t>
+          <t>3270171</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>541780</t>
+          <t>542083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550560</t>
+          <t>550561</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469227</t>
+          <t>470196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1015008</t>
+          <t>1014648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1025937</t>
+          <t>1025940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15028</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30430</t>
+          <t>29432</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,77 +2799,77 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>18622</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>944069</t>
+          <t>942367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>964758</t>
+          <t>964154</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2281960</t>
+          <t>2281903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2302370</t>
+          <t>2302303</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19471</t>
+          <t>19743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35794</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18899</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>41220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1907575</t>
+          <t>1908193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1933209</t>
+          <t>1934021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1745485</t>
+          <t>1746558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1755805</t>
+          <t>1755802</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3660442</t>
+          <t>3659471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3687297</t>
+          <t>3685844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>11879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>466716</t>
+          <t>464946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>480038</t>
+          <t>479466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>924111</t>
+          <t>923940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>938114</t>
+          <t>938091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35157</t>
+          <t>34649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25057</t>
+          <t>24142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>50162</t>
+          <t>50460</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>28690</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53885</t>
+          <t>53420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3334814</t>
+          <t>3335295</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3369554</t>
+          <t>3369297</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3542918</t>
+          <t>3542814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3552237</t>
+          <t>3552229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6884016</t>
+          <t>6884260</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6919031</t>
+          <t>6919970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>8852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20858</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>726822</t>
+          <t>727935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>744500</t>
+          <t>745729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>988881</t>
+          <t>987521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -6136,47 +6136,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1731495</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1720841</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>1738851</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>99,42%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1638</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1731495</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1718783</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1738623</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6484,34 +6484,34 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9799</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9799</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4498</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>17668</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11003</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29493</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>16334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17380</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>39346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2034944</t>
+          <t>2035206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2057238</t>
+          <t>2057270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1970883</t>
+          <t>1969726</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1983962</t>
+          <t>1983427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4014730</t>
+          <t>4014469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4039179</t>
+          <t>4037249</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4628</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,47 +7161,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>9736</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3979</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>19057</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>9736</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>19294</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>534297</t>
+          <t>532536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>545929</t>
+          <t>545915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534622</t>
+          <t>534066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>546344</t>
+          <t>546333</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1075976</t>
+          <t>1075715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1091080</t>
+          <t>1091144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,82 +7582,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>13802</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>7394</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>22553</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5295</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>13802</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>7070</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>22149</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>22478</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>47120</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34914</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>64161</t>
+          <t>64903</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3312448</t>
+          <t>3313852</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3340528</t>
+          <t>3342603</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3504497</t>
+          <t>3503845</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3522732</t>
+          <t>3521645</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6825273</t>
+          <t>6826539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6858925</t>
+          <t>6858730</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8249,22 +8249,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>12728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8309,7 +8309,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8319,32 +8319,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -8362,32 +8362,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8475,32 +8475,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13958</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8545,32 +8545,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>228904</t>
+          <t>242762</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>219017</t>
+          <t>233625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>234851</t>
+          <t>248592</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,27 +8623,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>295383</t>
+          <t>316808</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>284652</t>
+          <t>307705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301222</t>
+          <t>323241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8818,32 +8818,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8853,32 +8853,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8888,32 +8888,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>12379</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>689</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -9089,12 +9089,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>968503</t>
+          <t>1025361</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>959859</t>
+          <t>1013445</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>974342</t>
+          <t>1032297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>695142</t>
+          <t>542291</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>685141</t>
+          <t>531720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>701346</t>
+          <t>548509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1663644</t>
+          <t>1567652</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1652059</t>
+          <t>1554454</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1673196</t>
+          <t>1577321</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>548</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -9500,22 +9500,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>12682</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>334558</t>
+          <t>355736</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327284</t>
+          <t>348499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338513</t>
+          <t>360605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>237875</t>
+          <t>260690</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>233838</t>
+          <t>256201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>239914</t>
+          <t>263400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>572433</t>
+          <t>616426</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>564800</t>
+          <t>608145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>577438</t>
+          <t>622362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9956,22 +9956,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>5813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>24308</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>14970</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -10069,67 +10069,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>11394</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7248</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2153</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5943</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20437</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23705</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>15437</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1531964</t>
+          <t>1623858</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1517171</t>
+          <t>1609993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1541619</t>
+          <t>1635510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,67 +10330,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>999496</t>
+          <t>877027</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>989982</t>
+          <t>865385</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1007144</t>
+          <t>883926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2500885</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2483161</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2515260</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>97,74%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2531461</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2516151</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2547434</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
